--- a/artfynd/A 48464-2023 artfynd.xlsx
+++ b/artfynd/A 48464-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48464-2023 artfynd.xlsx
+++ b/artfynd/A 48464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,156 +816,6 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Kärlväxtinventering Värmlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>16959161</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1660</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lillängen, 700 m SSV om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>364447.833396154</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6632263.262711932</v>
-      </c>
-      <c r="S3" t="n">
-        <v>109</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Gunnarskog</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Arv-0670</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2014-02-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2014-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 660 bladrosetter med 16 blomstänglar, spridda grupper från 195-195 i sydväst till 126-255 i öster och 290-222 i norr</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre granskog med tallar, bitvis luckig och olikåldrig</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 48464-2023 artfynd.xlsx
+++ b/artfynd/A 48464-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7176418</v>
+        <v>7176416</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,17 +721,17 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillängen, 700 m SSV om, Vrm</t>
+          <t>Lillängen, 600 m SV om, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364447.3112820659</v>
+        <v>364311</v>
       </c>
       <c r="R2" t="n">
-        <v>6632262.778173422</v>
+        <v>6632434</v>
       </c>
       <c r="S2" t="n">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,24 +758,14 @@
           <t>2014-02-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-02-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 660 bladrosetter med 16 blomstänglar, spridda grupper från 195-195 i sydväst till 126-255 i öster och 290-222 i norr</t>
+          <t>170 bladrosetter med 1 blomstängel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +784,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre granskog med tallar, bitvis luckig och olikåldrig</t>
+          <t>mindre bestånd med äldre granar och enstaka tallar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,6 +799,137 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Värmlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7176418</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillängen, 700 m SSV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364447</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6632263</v>
+      </c>
+      <c r="S3" t="n">
+        <v>109</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-02-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-02-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 660 bladrosetter med 16 blomstänglar, spridda grupper från 195-195 i sydväst till 126-255 i öster och 290-222 i norr</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre granskog med tallar, bitvis luckig och olikåldrig</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Kärlväxtinventering Värmlands län</t>
         </is>
